--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -12354,7 +12354,7 @@
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46262.769384687504</v>
+        <v>46279.38265009259</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>411</v>
